--- a/assets/constructions/examples/ctd_mib_threadmill.xlsx
+++ b/assets/constructions/examples/ctd_mib_threadmill.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,11 +624,31 @@
           <t>zefp</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TM4SC-D42-16-3U</t>
+          <t>TMSH-D80-27-5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -638,12 +658,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TM4S</t>
+          <t>TMSH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VAR_TM_3/8U</t>
+          <t>VAR_TM_5/8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -665,12 +685,12 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -679,33 +699,31 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="W2" t="n">
-        <v>16</v>
-      </c>
-      <c r="X2" t="n">
-        <v>34</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
           <t>H7</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
@@ -726,12 +744,12 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx016</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>VARGUS_3/8U_TMSC</t>
+          <t>VARGUS_5/8T_TMC</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr"/>
@@ -745,36 +763,40 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1029.25</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>90453.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TMSH-D50-22-2</t>
+          <t>ASSN 080 065 A40-4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TMSH</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VAR_TM_1/4</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>40</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>7g/7H</t>
@@ -787,9 +809,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>8</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
@@ -802,57 +822,49 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="W3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>11</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AF3" t="b">
-        <v>0</v>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx022</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>VARGUS_1/4TEI_TM</t>
+          <t>PALB_A40</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr"/>
@@ -862,17 +874,23 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2018/VARGUS</t>
+          <t>2022/PALBIT Главный каталог</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>9</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TMSH-D125-40-5</t>
+          <t>RTMC-D44-22-25S6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -882,12 +900,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TMSH</t>
+          <t>MiTM 25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VAR_TM_5/8</t>
+          <t>VAR_*RT_25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -909,45 +927,47 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>BOTH</t>
-        </is>
-      </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V4" t="n">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="W4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X4" t="n">
         <v>40</v>
       </c>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
           <t>H7</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="AA4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
@@ -968,12 +988,12 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx040</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>VARGUS_5/8T_TMC</t>
+          <t>VARGUS_25N</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
@@ -987,26 +1007,50 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>902.85</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>79344.81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASSN 063 050 A30-4</t>
+          <t>RTMC-D48-22-41B5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PALBIT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>30</v>
-      </c>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MiTM 41</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VAR_*RT_41</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>7g/7H</t>
@@ -1019,11 +1063,13 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1035,38 +1081,48 @@
         <v>14</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>63</v>
+        <v>47.9</v>
       </c>
       <c r="W5" t="n">
         <v>22</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
       <c r="Z5" t="n">
         <v>50</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>41</v>
+      </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
           <t>ISO_6462:FDAxx022</t>
@@ -1074,7 +1130,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>PALB_A30</t>
+          <t>VARGUS_41N</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr"/>
@@ -1084,11 +1140,25 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2022/PALBIT Главный каталог</t>
+          <t>2018/VARGUS</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>812.59</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>71412.52</v>
       </c>
     </row>
     <row r="6">
@@ -1191,6 +1261,20 @@
       <c r="AM6" t="n">
         <v>4</v>
       </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1153.18</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>101344.46</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
